--- a/real_estate_forms/024_house_showing_checklist--real_estate_forms.xlsx
+++ b/real_estate_forms/024_house_showing_checklist--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1198,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>deadbolt</t>
+          <t>lock</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Deadbolt</t>
+          <t>Lock</t>
         </is>
       </c>
     </row>
@@ -2251,29 +2251,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>lock</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>locks_choices</t>
+          <t>plumbing_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>sinks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Sinks</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>sinks</t>
+          <t>toilets</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sinks</t>
+          <t>Toilets</t>
         </is>
       </c>
     </row>
@@ -2319,29 +2319,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>toilets</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Toilets</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>plumbing_choices</t>
+          <t>electrical_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Heat</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>heat</t>
+          <t>air_conditioning</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Air Conditioning</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>air_conditioning</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Air Conditioning</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -2387,29 +2387,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>electrical_choices</t>
+          <t>electrical_outlets_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2-3</t>
         </is>
       </c>
     </row>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-5</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>6-7</t>
         </is>
       </c>
     </row>
@@ -2489,27 +2489,10 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>8_or_more</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
-        <is>
-          <t>6-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>electrical_outlets_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>8_or_more</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
         <is>
           <t>8 or more</t>
         </is>
